--- a/assets/news/results/qualiperf_statistics.xlsx
+++ b/assets/news/results/qualiperf_statistics.xlsx
@@ -27,16 +27,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,21 +52,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,27 +428,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Qualiperf acknowledged</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -473,18 +461,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22 (66.7 %)</t>
+          <t>43 (78.2 %)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -494,18 +482,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7 (77.8 %)</t>
+          <t>11 (78.6 %)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -536,18 +524,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0 (0.0 %)</t>
+          <t>1 (12.5 %)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -557,18 +545,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19 (90.5 %)</t>
+          <t>25 (89.3 %)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -578,18 +566,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26 (78.8 %)</t>
+          <t>32 (80.0 %)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -599,18 +587,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4 (15.4 %)</t>
+          <t>6 (20.7 %)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -624,61 +612,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>IF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Authors Qualiperf</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Pubmed</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Journal_ID</t>
         </is>
@@ -701,9 +689,9 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E2" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>44416</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -754,9 +742,9 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E3" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>44416</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -807,9 +795,9 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>44461</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -860,9 +848,9 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E5" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>44150</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -882,7 +870,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -899,24 +887,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hepatectomy-Induced Alterations in Hepatic Perfusion and Function - Toward Multi-Scale Computational Modeling for a Better Prediction of Post-hepatectomy Liver Function</t>
+          <t>SBMLWebApp: Web-based Simulation, Steady-State Analysis, and Parameter Estimation of Systems Biology Models</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bruno Christ, Maximilian Collatz, Uta Dahmen, Karl-Heinz Herrmann, Sebastian Höpfl, Matthias König, Lena Lambers, Manja Marz, Daria Meyer, Nicole Radde, Jürgen R. Reichenbach, Tim Ricken and Hans-Michael Tautenhahn</t>
+          <t>Takahiro G. Yamada, Kaito Ii, Matthias König, Martina Feierabend, Andreas Dräger, Akira Funahashi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Front Physiol. 2021 Nov 18;12:733868. doi: 10.3389/fphys.2021.733868. PMID: 34867441; PMCID: PMC8637208</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>44518</v>
+          <t xml:space="preserve">Preprints 2021, 2021080259 (doi: 10.20944/preprints202108.0259.v1). [Submitted to MDPI, 2021-08-11] </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" s="1" t="n">
+        <v>44419</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -925,51 +911,51 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bruno Christ, Uta Dahmen, Karl-Heinz Herrmann, Sebastian Höpfl, Matthias König, Lena Lambers, Manja Marz, Daria Meyer, Nicole Erika Radde, Jürgen R. Reichenbach, Tim Ricken, Hans-Michael Tautenhahn</t>
+          <t>Matthias König</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P1 - Christ, P2 - Dahmen, P3 - König, P4 - Marz, P5 - Radde, P6 - Reichenbach, P7 - Ricken, P8 - Schwen, P9 - Tautenhahn, Coordination</t>
+          <t>P3 - König</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34867441/"&gt;34867441&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/ 10.3389/fphys.2021.733868"&gt; 10.3389/fphys.2021.733868&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/https://doi.org/10.3390/pr9101830"&gt;https://doi.org/10.3390/pr9101830&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Front Physiol</t>
+          <t>Processes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mesenchymal stromal cells mitigate liver damage after extended resection in the pig by modulating thrombospondin-1/TGF-β</t>
+          <t>Hepatectomy-Induced Alterations in Hepatic Perfusion and Function - Toward Multi-Scale Computational Modeling for a Better Prediction of Post-hepatectomy Liver Function</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nickel S*, Vlaic S*, Christ M*, Schubert K, Henschler R, Tautenhahn F, Burger C, Kühne H, Erler S, Roth A, Wild C, Brach J, Hammad S, Gittel C, Baunack M, Lange U, Broschewitz J, Stock P, Metelmann I, Bartels M, Pietsch U-C, Krämer S, Eichfeld U, von Bergen M, Dooley S*, Tautenhahn H-M*, Christ B*</t>
+          <t>Bruno Christ, Maximilian Collatz, Uta Dahmen, Karl-Heinz Herrmann, Sebastian Höpfl, Matthias König, Lena Lambers, Manja Marz, Daria Meyer, Nicole Radde, Jürgen R. Reichenbach, Tim Ricken and Hans-Michael Tautenhahn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NPJ Regen Med. 2021 Dec 3;6(1):84. doi: 10.1038/s41536-021-00194-4. PMID: 34862411; PMCID: PMC8642541</t>
+          <t>Front Physiol. 2021 Nov 18;12:733868. doi: 10.3389/fphys.2021.733868. PMID: 34867441; PMCID: PMC8637208</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>44533</v>
+        <v>3.4</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>44518</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -978,51 +964,51 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hans-Michael Tautenhahn*, Bruno Christ*</t>
+          <t>Bruno Christ, Uta Dahmen, Karl-Heinz Herrmann, Sebastian Höpfl, Matthias König, Lena Lambers, Manja Marz, Daria Meyer, Nicole Erika Radde, Jürgen R. Reichenbach, Tim Ricken, Hans-Michael Tautenhahn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P1 - Christ, P9 - Tautenhahn</t>
+          <t>P1 - Christ, P2 - Dahmen, P3 - König, P4 - Marz, P5 - Radde, P6 - Reichenbach, P7 - Ricken, P8 - Schwen, P9 - Tautenhahn, Coordination</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34862411/"&gt;34862411&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34867441/"&gt;34867441&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/ 10.1038/s41536-021-00194-4"&gt; 10.1038/s41536-021-00194-4&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/ 10.3389/fphys.2021.733868"&gt; 10.3389/fphys.2021.733868&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NPJ Regen Med</t>
+          <t>Front Physiol</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Semi-automated Data-driven FE Mesh Generation and InverseParameter Identification for a Multiscale and Multiphase Model ofFunction-Perfusion Processes in the Liver</t>
+          <t>Prediction of survival after hepatectomy using a physiologically based pharmacokinetic model of indocyanine green liver function tests</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lambers Lena, Mielke Andre, Ricken Tim</t>
+          <t>Adrian Köller, Jan Grzegorzewski, Michael Tautenhahn, Matthias König</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAMM·Proc. Appl. Math. Mech.2021;21:1 e202100190. doi: 10.1002/pamm.202100190</t>
+          <t>bioRxiv 2021.06.15.448411; doi: https://doi.org/10.1101/2021.06.15.448411, [Submitted to Frontiers Physiology 2021-06-30]</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>44462</v>
+        <v>3.4</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>44377</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1031,51 +1017,51 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lena Lambers, Tim Ricken</t>
+          <t>Adrian Köller, Jan Grzegorzweski, Hans-Michael Tautenhahn, Matthias König</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P7 - Ricken, Coordination</t>
+          <t>P3 - König</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34880771/"&gt;34880771&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1002/pamm.202100190"&gt;10.1002/pamm.202100190&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/doi.org/10.3389/fphys.2021.730418 "&gt;doi.org/10.3389/fphys.2021.730418 &lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PAMM Proc Appl Math Mech</t>
+          <t>Front Physiol</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Greasy hair against obesity</t>
+          <t>Mesenchymal stromal cells mitigate liver damage after extended resection in the pig by modulating thrombospondin-1/TGF-β</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nickel S, Christ B</t>
+          <t>Nickel S*, Vlaic S*, Christ M*, Schubert K, Henschler R, Tautenhahn F, Burger C, Kühne H, Erler S, Roth A, Wild C, Brach J, Hammad S, Gittel C, Baunack M, Lange U, Broschewitz J, Stock P, Metelmann I, Bartels M, Pietsch U-C, Krämer S, Eichfeld U, von Bergen M, Dooley S*, Tautenhahn H-M*, Christ B*</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Signal Transduction and Targeted Therapy (2021)6:429; https://doi.org/10.1038/s41392-021-00850-7</t>
+          <t>NPJ Regen Med. 2021 Dec 3;6(1):84. doi: 10.1038/s41536-021-00194-4. PMID: 34862411; PMCID: PMC8642541</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>44547</v>
+        <v>6.5</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>44533</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1084,51 +1070,51 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bruno Christ</t>
+          <t>Hans-Michael Tautenhahn*, Bruno Christ*</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P1 - Christ</t>
+          <t>P1 - Christ, P9 - Tautenhahn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34921132/"&gt;34921132&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34862411/"&gt;34862411&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1038/s41392-021-00850-7"&gt;10.1038/s41392-021-00850-7&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/ 10.1038/s41536-021-00194-4"&gt; 10.1038/s41536-021-00194-4&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Signal Transduction and Targeted Therapy</t>
+          <t>NPJ Regen Med</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Theoretical formulation and computational aspects of a two-scale homogenization scheme combining the TPM and FE2 method for poro-elastic fuid-saturated porous media</t>
+          <t>Semi-automated Data-driven FE Mesh Generation and InverseParameter Identification for a Multiscale and Multiphase Model ofFunction-Perfusion Processes in the Liver</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ricken Tim, Schröder Jörg, Bluhm Joachim, Maike Simon, Bartel Florian</t>
+          <t>Lambers Lena, Mielke Andre, Ricken Tim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>International Journal of Solid and Structures</t>
+          <t xml:space="preserve"> PAMM·Proc. Appl. Math. Mech.2021;21:1 e202100190. doi: 10.1002/pamm.202100190</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>44206</v>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>44462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1137,60 +1123,60 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tim Ricken</t>
+          <t>Lena Lambers, Tim Ricken</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P7 - Ricken</t>
+          <t>P7 - Ricken, Coordination</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1016/j.ijsolstr.2021.111412"&gt;10.1016/j.ijsolstr.2021.111412&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1002/pamm.202100190"&gt;10.1002/pamm.202100190&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>International Journal of Solid and Structures</t>
+          <t>PAMM Proc Appl Math Mech</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ramipril Reduces Acylcarnitines and Distinctly Increases Angiotensin-Converting Enzyme 2 Expression in Lungs of Rats</t>
+          <t>Greasy hair against obesity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kosacka J*, Berger C, Ceglarek U, Hoffmann A, Blüher M, Klöting N </t>
+          <t>Nickel S, Christ B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metabolites. 2022 Mar 26;12(4):293. doi: 10.3390/metabo12040293. PMID: 35448480; PMCID: PMC9028516.</t>
+          <t>Signal Transduction and Targeted Therapy (2021)6:429; https://doi.org/10.1038/s41392-021-00850-7</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>44646</v>
+        <v>40.8</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>44547</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Joanna Kosacka</t>
+          <t>Bruno Christ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1200,41 +1186,41 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35448480/"&gt;35448480&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34921132/"&gt;34921132&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.3390/metabo12040293"&gt;10.3390/metabo12040293&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1038/s41392-021-00850-7"&gt;10.1038/s41392-021-00850-7&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Metabolites</t>
+          <t>Signal Transduction and Targeted Therapy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specifications of standards in systems and synthetic biology: status and developments in 2021</t>
+          <t>Theoretical formulation and computational aspects of a two-scale homogenization scheme combining the TPM and FE2 method for poro-elastic fuid-saturated porous media</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Falk Schreiber, Padraig Gleeson, Martin Golebiewski, Thomas E. Gorochowski, Michael Hucka, Sarah M. Keating, Matthias König, Chris J. Myers, David P. Nickerson, Björn Sommer, Dagmar Waltemath</t>
+          <t>Ricken Tim, Schröder Jörg, Bluhm Joachim, Maike Simon, Bartel Florian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J Integr Bioinform. 2021 Oct 22;18(3):20210026. doi: 10.1515/jib-2021-0026. PMID: 34674411; PMCID: PMC8573232. https://doi.org/10.1515/jib-2021-0026</t>
+          <t>International Journal of Solid and Structures</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>44491</v>
+        <v>3.8</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>44206</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1243,424 +1229,424 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthias König </t>
+          <t>Tim Ricken</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P3 - König</t>
+          <t>P7 - Ricken</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34674411/"&gt;34674411&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1515/jib-2021-0026"&gt;10.1515/jib-2021-0026&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1016/j.ijsolstr.2021.111412"&gt;10.1016/j.ijsolstr.2021.111412&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>J Integr Bioinform</t>
+          <t>International Journal of Solid and Structures</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Editorial: Computational Modeling for Liver Surgery and Interventions</t>
+          <t>The Systems Biology Simulation Core Library</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bruno Christ, Uta Dahmen, Nicole Radde, Tim Ricken</t>
+          <t>Panchiwala, H.; Shah, S.; Planatscher, H.; Zakharchuk, M.; König, M.; Dräger, A.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Front Physiol. 2022 Feb 15;13:859522. doi: 10.3389/fphys.2022.859522. PMID: 35242057; PMCID: PMC8886156</t>
+          <t xml:space="preserve">Preprints 2020, 2020120296 (doi: 10.20944/preprints202012.0296.v1), [In revision, Bioinformatics] </t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>44664</v>
+        <v>5.4</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>44176</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bruno Christ, Uta Dahmen, Nicole Erika Radde, Tim Ricken</t>
+          <t>Matthias König</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P1 - Christ, P2 - Dahmen, P5 - Radde, P7 - Ricken</t>
+          <t>P3 - König</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35242057/"&gt;35242057&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34554191/"&gt;34554191&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.3389/fphys.2022.859522"&gt;10.3389/fphys.2022.859522&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/doi.org/10.1093/bioinformatics/btab669"&gt;doi.org/10.1093/bioinformatics/btab669&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Front Physiol</t>
+          <t>Bioinformatics</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Pharmacokinetics of caffeine: A systematic analysis of reported data for application in metabolic phenotyping and liver function testing</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jan Grzegorzewski, Florian Bartsch, Adrian Köller, Matthias König</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bioRxiv 2021.07.12.452094; doi: https://doi.org/10.1101/2021.07.12.452094 [Submitted to Frontiers Pharmacology, 2021-08-03]</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>44411</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Jan Grzergorzweski, Florian Bartsch, Adrian Köller, Matthias König</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>P3 - König</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35280254/"&gt;35280254&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1101/2021.07.12.452094"&gt;10.1101/2021.07.12.452094&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Front Pharmacol</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ramipril Reduces Acylcarnitines and Distinctly Increases Angiotensin-Converting Enzyme 2 Expression in Lungs of Rats</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kosacka J*, Berger C, Ceglarek U, Hoffmann A, Blüher M, Klöting N </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Metabolites. 2022 Mar 26;12(4):293. doi: 10.3390/metabo12040293. PMID: 35448480; PMCID: PMC9028516.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>44646</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Joanna Kosacka</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P1 - Christ</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35448480/"&gt;35448480&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3390/metabo12040293"&gt;10.3390/metabo12040293&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metabolites</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Specifications of standards in systems and synthetic biology: status and developments in 2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Falk Schreiber, Padraig Gleeson, Martin Golebiewski, Thomas E. Gorochowski, Michael Hucka, Sarah M. Keating, Matthias König, Chris J. Myers, David P. Nickerson, Björn Sommer, Dagmar Waltemath</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>J Integr Bioinform. 2021 Oct 22;18(3):20210026. doi: 10.1515/jib-2021-0026. PMID: 34674411; PMCID: PMC8573232. https://doi.org/10.1515/jib-2021-0026</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>44491</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matthias König </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P3 - König</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34674411/"&gt;34674411&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1515/jib-2021-0026"&gt;10.1515/jib-2021-0026&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>J Integr Bioinform</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Editorial: Computational Modeling for Liver Surgery and Interventions</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bruno Christ, Uta Dahmen, Nicole Radde, Tim Ricken</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Front Physiol. 2022 Feb 15;13:859522. doi: 10.3389/fphys.2022.859522. PMID: 35242057; PMCID: PMC8886156</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>44664</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bruno Christ, Uta Dahmen, Nicole Erika Radde, Tim Ricken</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>P1 - Christ, P2 - Dahmen, P5 - Radde, P7 - Ricken</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35242057/"&gt;35242057&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3389/fphys.2022.859522"&gt;10.3389/fphys.2022.859522&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Front Physiol</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>QuaLiPerF - Multi-X Liver Modelling</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Tim Ricken, Lena Lambers, Bruno Christ, Uta Dahmen, Karl-Heinz Herrmann, Matthias König, Manja Marz, Nicole Radde, Jürgen R. Reichenbach, Lars Ole Schwen, and Hans-Michael Tautenhahn</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GACM-Report</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>44175</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Tim Ricken, Lena Lambers, Bruno Christ, Uta Dahmen, Karl-Heinz Herrmann, Matthias König
 König, Manja Marz, Nicole Radde, Jürgen R. Reichenbach, Lars Ole Schwen, and
 Hans-Michael Tautenhahn</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>P1 - Christ, P2 - Dahmen, P3 - König, P4 - Marz, P5 - Radde, P6 - Reichenbach, P7 - Ricken, P8 - Schwen, P9 - Tautenhahn, Coordination</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>&lt;a href="https://doi.org/-"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>GACM-Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Streptozotocin-Induced Diabetes Causes Changes in Serotonin-Positive Neurons in the Small Intestine in Pig Model</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulc, M.; Palus, K.; Całka, J.; Kosacka, J.; Nowicki, M. </t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Int J Mol Sci. 2022 Apr 20;23(9):4564. doi: 10.3390/ijms23094564. PMID: 35562954; PMCID: PMC9099899</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>44671</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Joanna Kosacka</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>P1 - Christ</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35562954/"&gt;35562954&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://doi.org/10.3390/ijms23094564"&gt;10.3390/ijms23094564&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Int J Mol Sci</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BioSimulators: a central registry of simulation engines and services for recommending specific tools</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Shaikh B, Smith LP, Vasilescu D, Marupilla G, Wilson M, Agmon E, Agnew H, Andrews SS, Anwar A, Beber ME, Bergmann FT, Brooks D, Brusch L, Calzone L, Choi K, Cooper J, Detloff J, Drawert B, Dumontier M, Ermentrout GB, Faeder JR, Freiburger AP, Fröhlich F, Funahashi A, Garny A, Gennari JH, Gleeson P, Goelzer A, Haiman Z, Hasenauer J, Hellerstein JL, Hermjakob H, Hoops S, Ison JC, Jahn D, Jakubowski HV, Jordan R, Kalaš M, König M, Liebermeister W, Sheriff RSM, Mandal S, McDougal R, Medley JK, Mendes P, Müller R, Myers CJ, Naldi A, Nguyen TVN, Nickerson DP, Olivier BG, Patoliya D, Paulevé L, Petzold LR, Priya A, Rampadarath AK, Rohwer JM, Saglam AS, Singh D, Sinha A, Snoep J, Sorby H, Spangler R, Starruß J, Thomas PJ, van Niekerk D, Weindl D, Zhang F, Zhukova A, Goldberg AP, Schaff JC, Blinov ML, Sauro HM, Moraru II, Karr JR.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nucleic Acids Res. 2022 Jul 5;50(W1):W108-W114. doi: 10.1093/nar/gkac331. PMID: 35524558; PMCID: PMC9252793</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>44688</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Matthias König</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>P3 - König</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35524558/"&gt;35524558&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://doi.org/10.1093/nar/gkac331"&gt;10.1093/nar/gkac331&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Nucleic Acids Res</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Human Mesenchymal Stromal Cells Resolve Lipid Load in High Fat Diet‐Induced Non‐Alcoholic  Steatohepatitis in Mice by Mitochondria Donation</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Sandra Nickel, Madlen Christ, Sandra Schmidt, Joanna Kosacka, Hagen Kühne, Martin Roderfeld, Thomas Longerich, Lysann Tietze, Ina Bosse, Mei‐Ju Hsu, Peggy Stock, Elke Roeb, Bruno Christ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Cells. 2022 Jun 2;11(11):1829. doi: 10.3390/cells11111829. PMID: 35681524; PMCID: PMC9180625</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>44714</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joanna Kosacka, Lysann Tietze, Bruno Christ </t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>P1 - Christ</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35681524/"&gt;35681524&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://doi.org/10.3390/cells11111829"&gt;10.3390/cells11111829&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model-based design of a synthetic oscillator based on an epigenetic methylation memory system</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Viviane Klingel, Dimitri Graf, Sara Weirich, Albert Jeltsch, Nicole E. Radde</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ACS Synth Biol. 2022 Jul 15;11(7):2445-2455. doi: 10.1021/acssynbio.2c00118. Epub 2022 Jun 24. PMID: 35749318; PMCID: PMC9295699</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>44714</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nicole Erika Radde </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>P5 - Radde</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35749318/"&gt;35749318&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://doi.org/ 10.1021/acssynbio.2c00118"&gt; 10.1021/acssynbio.2c00118&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>ACS Synth Biol</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>An inverse transformation algorithm to infer parameter distributions from population snapshot data</t>
+          <t>Streptozotocin-Induced Diabetes Causes Changes in Serotonin-Positive Neurons in the Small Intestine in Pig Model</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vincent Wagner, Sebastian Höpfl, Viviane Klingel, Maria C. Pop, Nicole E. Radde</t>
+          <t xml:space="preserve">Bulc, M.; Palus, K.; Całka, J.; Kosacka, J.; Nowicki, M. </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IFAC-PapersOnLine, 9th IFAC Conference on Foundations of Systems Biology in Engineering FOSBE 2022, https://doi.org/10.1016/j.ifacol.2023.01.020</t>
+          <t>Int J Mol Sci. 2022 Apr 20;23(9):4564. doi: 10.3390/ijms23094564. PMID: 35562954; PMCID: PMC9099899</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>44714</v>
+        <v>4.9</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>44671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sebastian Höpfl, Nicole Erika Radde</t>
+          <t>Joanna Kosacka</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P5 - Radde</t>
+          <t>P1 - Christ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35562954/"&gt;35562954&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1016/j.ifacol.2023.01.020"&gt;10.1016/j.ifacol.2023.01.020&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.3390/ijms23094564"&gt;10.3390/ijms23094564&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>IFAC-PapersOnLine</t>
+          <t>Int J Mol Sci</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Multimodale Therapie bei Lebermetastasen kolorektaler Karzinome in kurativer Intention</t>
+          <t>BioSimulators: a central registry of simulation engines and services for recommending specific tools</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">PD Dr. med. Hans-Michael Tautenhahn, Sandra Nickel, Eva Maria Kindler, Utz Settmacher </t>
+          <t>Shaikh B, Smith LP, Vasilescu D, Marupilla G, Wilson M, Agmon E, Agnew H, Andrews SS, Anwar A, Beber ME, Bergmann FT, Brooks D, Brusch L, Calzone L, Choi K, Cooper J, Detloff J, Drawert B, Dumontier M, Ermentrout GB, Faeder JR, Freiburger AP, Fröhlich F, Funahashi A, Garny A, Gennari JH, Gleeson P, Goelzer A, Haiman Z, Hasenauer J, Hellerstein JL, Hermjakob H, Hoops S, Ison JC, Jahn D, Jakubowski HV, Jordan R, Kalaš M, König M, Liebermeister W, Sheriff RSM, Mandal S, McDougal R, Medley JK, Mendes P, Müller R, Myers CJ, Naldi A, Nguyen TVN, Nickerson DP, Olivier BG, Patoliya D, Paulevé L, Petzold LR, Priya A, Rampadarath AK, Rohwer JM, Saglam AS, Singh D, Sinha A, Snoep J, Sorby H, Spangler R, Starruß J, Thomas PJ, van Niekerk D, Weindl D, Zhang F, Zhukova A, Goldberg AP, Schaff JC, Blinov ML, Sauro HM, Moraru II, Karr JR.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chirurgie (Heidelb). 2022 Jul;93(7):652-658. German. doi: 10.1007/s00104-022-01665-0. Epub 2022 Jun 8. PMID: 35771270</t>
+          <t>Nucleic Acids Res. 2022 Jul 5;50(W1):W108-W114. doi: 10.1093/nar/gkac331. PMID: 35524558; PMCID: PMC9252793</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>44720</v>
+        <v>16.6</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>44688</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1669,27 +1655,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hans-Michael Tautenhahn, Eva Maria Kindler</t>
+          <t>Matthias König</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P9 - Tautenhahn</t>
+          <t>P3 - König</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35771270/"&gt;35771270&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35524558/"&gt;35524558&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1007/s00104-022-01665-0"&gt;10.1007/s00104-022-01665-0&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1093/nar/gkac331"&gt;10.1093/nar/gkac331&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Chirurgie</t>
+          <t>Nucleic Acids Res</t>
         </is>
       </c>
     </row>
@@ -1701,19 +1687,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wagner V, Castellaz B, Oesting M, Radde N</t>
+          <t>Vincent Wagner, Benjamin Castellaz, Marco Oesting, Nicole Radde</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bioinformatics. 2022 Sep 15;38(18):4352-4359. doi: 10.1093/bioinformatics/btac501. PMID: 35916726</t>
+          <t xml:space="preserve">BioRxiv 2021.12.01.470753 doi: https://doi.org/10.1101/2021.12.01.470753 </t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>44760</v>
+        <v>5.4</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>44532</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1749,24 +1735,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>On robust discretization methods for poroelastic problems: Numerical examples and counter-examples</t>
+          <t>Physiologically based pharmacokinetic (PBPK) modeling of the role of CYP2D6 polymorphism for metabolic phenotyping with dextromethorphan</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fleurianne Bertrand ,Maximilian Brodbeck, Tim Ricken</t>
+          <t>Grzegorzewski J., Brandhorst J., König M.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Examples and Counterexamples,  https://doi.org/10.1016/j.exco.2022.100087</t>
+          <t>bioRxiv 2022.08.23.504981; doi: https://doi.org/10.1101/2022.08.23.504981</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>44832</v>
+        <v>4.4</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>44799</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1775,51 +1761,51 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tim Ricken </t>
+          <t>Jan Grzegorzewski, Janosch Brandhorst, Matthias König</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P7 - Ricken</t>
+          <t>P3 - König</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36353484/"&gt;36353484&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1016/j.exco.2022.100087"&gt;10.1016/j.exco.2022.100087&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.3389/fphar.2022.1029073 "&gt;10.3389/fphar.2022.1029073 &lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Examples and Counterexamples</t>
+          <t>Front Pharmacol</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>libRoadRunner 2.0: A High-Performance SBML Simulation and Analysis Library</t>
+          <t>Human Mesenchymal Stromal Cells Resolve Lipid Load in High Fat Diet‐Induced Non‐Alcoholic  Steatohepatitis in Mice by Mitochondria Donation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ciaran Welsh, Jin Xu, Lucian Smith, Matthias König, Kiri Choi, Herbert M. Sauro</t>
+          <t>Sandra Nickel, Madlen Christ, Sandra Schmidt, Joanna Kosacka, Hagen Kühne, Martin Roderfeld, Thomas Longerich, Lysann Tietze, Ina Bosse, Mei‐Ju Hsu, Peggy Stock, Elke Roeb, Bruno Christ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bioinformatics. 2022 Dec 8:btac770. doi: 10.1093/bioinformatics/btac770. Epub ahead of print. PMID: 36478036.</t>
+          <t>Cells. 2022 Jun 2;11(11):1829. doi: 10.3390/cells11111829. PMID: 35681524; PMCID: PMC9180625</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>44903</v>
+        <v>5.2</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>44714</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1828,51 +1814,51 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Matthias König</t>
+          <t xml:space="preserve">Joanna Kosacka, Lysann Tietze, Bruno Christ </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P3 - König</t>
+          <t>P1 - Christ</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36478036/"&gt;36478036&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35681524/"&gt;35681524&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1093/bioinformatics/btac770"&gt;10.1093/bioinformatics/btac770&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.3390/cells11111829"&gt;10.3390/cells11111829&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Bioinformatics</t>
+          <t>Cells</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Periportal steatosis in mice affects distinct parameters of pericentral drug metabolism </t>
+          <t>Model-based design of a synthetic oscillator based on an epigenetic methylation memory system</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Albadry M.,  Höpfl, S., Ehteshamzad, N., König, M., Böttcher, M., Neumann, J., Lupp, A., Dirsch, O., Radde, N., Christ, B., Christ, M., Schwen, L. O., Laue, H., Klopfleisch, R., Dahmen, U.</t>
+          <t>Viviane Klingel, Dimitri Graf, Sara Weirich, Albert Jeltsch, Nicole E. Radde</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sci Rep. 2022 Dec 17;12(1):21825. doi: 10.1038/s41598-022-26483-6. PMID: 36528753; PMCID: PMC9759570</t>
+          <t>ACS Synth Biol. 2022 Jul 15;11(7):2445-2455. doi: 10.1021/acssynbio.2c00118. Epub 2022 Jun 24. PMID: 35749318; PMCID: PMC9295699</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>44912</v>
+        <v>3.9</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>44714</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1881,51 +1867,51 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mohamed Albadry, Sebastian Höpfl, Matthias König, Nicole Erika Radde, Bruno Christ, Lars Ole Schwen, Uta Dahmen</t>
+          <t xml:space="preserve">Nicole Erika Radde </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P1 - Christ, P2 - Dahmen, P3 - König, P5 - Radde, P8 - Schwen</t>
+          <t>P5 - Radde</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36528753/"&gt;36528753&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35749318/"&gt;35749318&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1038/s41598-022-26483-6"&gt;10.1038/s41598-022-26483-6&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/ 10.1021/acssynbio.2c00118"&gt; 10.1021/acssynbio.2c00118&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Sci Rep</t>
+          <t>ACS Synth Biol</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uncertainty with Varying Subsurface Permeabilities Reduced Using Coupled Random Field and Extended Theory of Porous Media Contaminant Transport Models</t>
+          <t>An inverse transformation algorithm to infer parameter distributions from population snapshot data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S. M. Seyedpour, C. Henning, P. Kirmizakis, S. Herbrandt, K. Ickstadt, R. Doherty and T. Ricken</t>
+          <t>Vincent Wagner, Sebastian Höpfl, Viviane Klingel, Maria C. Pop, Nicole E. Radde</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Water 2023, 15, 159. https://doi.org/10.3390/w15010159</t>
+          <t>IFAC-PapersOnLine, 9th IFAC Conference on Foundations of Systems Biology in Engineering FOSBE 2022, https://doi.org/10.1016/j.ifacol.2023.01.020</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>44926</v>
+        <v>1.2</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>44714</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1934,104 +1920,100 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tim Ricken</t>
+          <t>Sebastian Höpfl, Nicole Erika Radde</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P7 - Ricken</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
-        </is>
-      </c>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.3390/w15010159"&gt;10.3390/w15010159&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1016/j.ifacol.2023.01.020"&gt;10.1016/j.ifacol.2023.01.020&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>IFAC-PapersOnLine</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Simulation of Contaminant Transport through the Vadose Zone: A Continuum Mechanical Approach within the Framework of the Extended Theory of Porous Media (eTPM)</t>
+          <t>Multimodale Therapie bei Lebermetastasen kolorektaler Karzinome in kurativer Intention</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S. M. Seyedpour, A. Thom and T. Ricken</t>
+          <t xml:space="preserve">PD Dr. med. Hans-Michael Tautenhahn, Sandra Nickel, Eva Maria Kindler, Utz Settmacher </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Water 2023, 15, 343. https://doi.org/10.3390/w15020343</t>
+          <t>Chirurgie (Heidelb). 2022 Jul;93(7):652-658. German. doi: 10.1007/s00104-022-01665-0. Epub 2022 Jun 8. PMID: 35771270</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>44939</v>
+        <v>0.6</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>44720</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tim Ricken</t>
+          <t>Hans-Michael Tautenhahn, Eva Maria Kindler</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P7 - Ricken</t>
+          <t>P9 - Tautenhahn</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov//"&gt;&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35771270/"&gt;35771270&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.3390/w15020343"&gt;10.3390/w15020343&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1007/s00104-022-01665-0"&gt;10.1007/s00104-022-01665-0&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Chirurgie</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bayesian estimation reveals that reproducible models in Systems Biology get more citations</t>
+          <t>Quasi-Entropy Closure: A Fast and Reliable Approach to Close the Moment Equations of the Chemical Master Equation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Höpfl Sebastian, Pleiss Jürgen, Radde Nicole</t>
+          <t>Wagner V, Castellaz B, Oesting M, Radde N</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sci Rep 13, 2695 (2023). https://doi.org/10.1038/s41598-023-29340-2</t>
+          <t>Bioinformatics. 2022 Sep 15;38(18):4352-4359. doi: 10.1093/bioinformatics/btac501. PMID: 35916726</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>44972</v>
+        <v>5.4</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>44760</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2040,7 +2022,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sebastian Höpfl, Nicole Erika Radde</t>
+          <t xml:space="preserve">Nicole Erika Radde </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2050,94 +2032,90 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36792648/"&gt;36792648&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35916726/"&gt;35916726&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1038/s41598-023-29340-2"&gt;10.1038/s41598-023-29340-2&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/ 10.1093/bioinformatics/btac501"&gt; 10.1093/bioinformatics/btac501&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Sci Rep</t>
+          <t>Bioinformatics</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Critical Evaluation of Discarded Donor Livers  in the Eurotransplant Region: Potential  Implications for Machine Perfusion</t>
+          <t>On robust discretization methods for poroelastic problems: Numerical examples and counter-examples</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Falk Rauchfuß, Hans-Michael Tautenhahn, Felix Dondorf, Aladdin Ali-Deeb, Utz Settmacher on behalf of the ELIAC</t>
+          <t>Fleurianne Bertrand ,Maximilian Brodbeck, Tim Ricken</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>e-ISSN 2329-0358 © Ann Transplant, 2023; 28: e938132 DOI: 10.12659/AOT.938132</t>
+          <t>Examples and Counterexamples,  https://doi.org/10.1016/j.exco.2022.100087</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>44990</v>
+        <v>0.7</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>44832</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans-Michael Tautenhahn </t>
+          <t xml:space="preserve">Tim Ricken </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P9 - Tautenhahn</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36927714/"&gt;36927714&lt;/a&gt;</t>
-        </is>
-      </c>
+          <t>P7 - Ricken</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/ 10.12659/AOT.938132"&gt; 10.12659/AOT.938132&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1016/j.exco.2022.100087"&gt;10.1016/j.exco.2022.100087&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ann Transplant</t>
+          <t>Examples and Counterexamples</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specifications of Standards in Systems and Synthetic Biology: Status and Developments in 2022 and the COMBINE meeting 2022</t>
+          <t>Physiologically based modeling of the effect of physiological and anthropometric variability on indocyanine green based liver function tests</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M. König, P. Gleeson, M. Golebiewski, T. Gorochowski, M. Hucka, S. Keating, C. Myers, D. Nickerson, F. Schreiber</t>
+          <t>Adrian Köller, Jan Grzegorzewski and Matthias König</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>J Integr Bioinform. 2023 Mar 29;20(1):20230004. doi: 10.1515/jib-2023-0004. PMID: 36989443; PMCID: PMC10063176</t>
+          <t>bioRxiv 2021.08.11.455999; doi: https://doi.org/10.1101/2021.08.11.455999 [Submitted to Frontiers Physiology 2021-08-12]</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>45014</v>
+        <v>3.4</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>44420</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2146,7 +2124,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Matthias König</t>
+          <t>Adrian Köller, Matthias König</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2156,200 +2134,196 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36989443/"&gt;36989443&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/34880776/"&gt;34880776&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1515/jib-2023-0004"&gt;10.1515/jib-2023-0004&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1101/2021.08.11.455999"&gt;10.1101/2021.08.11.455999&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>J Integr Bioinform</t>
+          <t>Front Physiol</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Editorial: Multiscale modeling for the liver</t>
+          <t>libRoadRunner 2.0: A High-Performance SBML Simulation and Analysis Library</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ho H, Rezania V, Schwen LO</t>
+          <t>Ciaran Welsh, Jin Xu, Lucian Smith, Matthias König, Kiri Choi, Herbert M. Sauro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Front. Bioeng. Biotechnol. 2023 Apr 13;1179980. doi:10.3389/fbioe.2023.1179980</t>
+          <t>Bioinformatics. 2022 Dec 8:btac770. doi: 10.1093/bioinformatics/btac770. Epub ahead of print. PMID: 36478036.</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>45029</v>
+        <v>5.4</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>44903</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lars Ole Schwen</t>
+          <t>Matthias König</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P8 - Schwen</t>
+          <t>P3 - König</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37122862/"&gt;37122862&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36478036/"&gt;36478036&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.3389/fbioe.2023.1179980 "&gt;10.3389/fbioe.2023.1179980 &lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1093/bioinformatics/btac770"&gt;10.1093/bioinformatics/btac770&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Front Bioeng Biotechnol</t>
+          <t>Bioinformatics</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Automated Detection of Portal Fields and Central Veins in Whole-Slide Images of Liver Tissue</t>
+          <t xml:space="preserve">Periportal steatosis in mice affects distinct parameters of pericentral drug metabolism </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Budelmann D, Laue H, Weis N, Dahmen U, D’Alessandro LA, Biermayer I, Klingmüller U, Ghallab A, Hassan R, Begher-Tibbe B, Hengstler JG, Schwen LO</t>
+          <t>Albadry M.,  Höpfl, S., Ehteshamzad, N., König, M., Böttcher, M., Neumann, J., Lupp, A., Dirsch, O., Radde, N., Christ, B., Christ, M., Schwen, L. O., Laue, H., Klopfleisch, R., Dahmen, U.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Journal of Pathology Informatics 2022 13:100001, doi: 10.1016/j.jpi.2022.100001</t>
+          <t>Sci Rep. 2022 Dec 17;12(1):21825. doi: 10.1038/s41598-022-26483-6. PMID: 36528753; PMCID: PMC9759570</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>44606</v>
+        <v>3.9</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>44912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(None received QuaLiPerF funding for this work)</t>
+          <t>Mohamed Albadry, Sebastian Höpfl, Matthias König, Nicole Erika Radde, Bruno Christ, Lars Ole Schwen, Uta Dahmen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Stea-PK Mod</t>
+          <t>P1 - Christ, P2 - Dahmen, P3 - König, P5 - Radde, P8 - Schwen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35242441/"&gt;35242441&lt;/a&gt;</t>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36528753/"&gt;36528753&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1016/j.jpi.2022.100001"&gt;10.1016/j.jpi.2022.100001&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.1038/s41598-022-26483-6"&gt;10.1038/s41598-022-26483-6&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Journal of Pathology Informatics</t>
+          <t>Sci Rep</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Perfusion and T2 Relaxation Time as Predictors of Severity and Outcome in Sepsis-Associated Acute Kidney Injury: A Preclinical MRI Study</t>
+          <t>Uncertainty with Varying Subsurface Permeabilities Reduced Using Coupled Random Field and Extended Theory of Porous Media Contaminant Transport Models</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zhao, W.-T, Herrmann, K.-H., Sibgatulin R., Nahardani A., Krämer M., Heitplatz B., Van Marck V. , Reuter S., Reichenbach J.R., Hoerr V.</t>
+          <t>S. M. Seyedpour, C. Henning, P. Kirmizakis, S. Herbrandt, K. Ickstadt, R. Doherty and T. Ricken</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>J Magn Reson Imaging 2023 Apr 7. doi: 10.1002/jmri.28698</t>
+          <t>Water 2023, 15, 159. https://doi.org/10.3390/w15010159</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>45111</v>
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>44926</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Wan-Ting Zhao, Karl-Heinz Herrmann, Jürgen R. Reichenbach</t>
+          <t>Tim Ricken</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P6 - Reichenbach</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37026419/"&gt;37026419&lt;/a&gt;</t>
-        </is>
-      </c>
+          <t>P7 - Ricken</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.1002/jmri.28698"&gt;10.1002/jmri.28698&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.3390/w15010159"&gt;10.3390/w15010159&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>J Magn Reson Imaging</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A pathway model of glucose-stimulated insulin secretion in the pancreatic β-cell</t>
+          <t>Simulation of Contaminant Transport through the Vadose Zone: A Continuum Mechanical Approach within the Framework of the Extended Theory of Porous Media (eTPM)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Maheshvare MD., Raha S., König M.*, and Pal D.* (* equal contribution)</t>
+          <t>S. M. Seyedpour, A. Thom and T. Ricken</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Front. Endocrinol. 14:1185656, doi: 10.3389/fendo.2023.1185656</t>
+          <t>Water 2023, 15, 343. https://doi.org/10.3390/w15020343</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>44965</v>
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>44939</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2358,80 +2332,1228 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Matthias König</t>
+          <t>Tim Ricken</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P3 - König</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37600713/"&gt;37600713&lt;/a&gt;</t>
-        </is>
-      </c>
+          <t>P7 - Ricken</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.3389/fendo.2023.1185656 "&gt;10.3389/fendo.2023.1185656 &lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/10.3390/w15020343"&gt;10.3390/w15020343&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Front Endocrinol</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Bayesian estimation reveals that reproducible models in Systems Biology get more citations</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Pleiss Jürgen, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sci Rep 13, 2695 (2023). https://doi.org/10.1038/s41598-023-29340-2</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>44972</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sebastian Höpfl, Nicole Erika Radde</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36792648/"&gt;36792648&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1038/s41598-023-29340-2"&gt;10.1038/s41598-023-29340-2&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Sci Rep</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Critical Evaluation of Discarded Donor Livers  in the Eurotransplant Region: Potential  Implications for Machine Perfusion</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Falk Rauchfuß, Hans-Michael Tautenhahn, Felix Dondorf, Aladdin Ali-Deeb, Utz Settmacher on behalf of the ELIAC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>e-ISSN 2329-0358 © Ann Transplant, 2023; 28: e938132 DOI: 10.12659/AOT.938132</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>44990</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hans-Michael Tautenhahn </t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36927714/"&gt;36927714&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/ 10.12659/AOT.938132"&gt; 10.12659/AOT.938132&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ann Transplant</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Specifications of Standards in Systems and Synthetic Biology: Status and Developments in 2022 and the COMBINE meeting 2022</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M. König, P. Gleeson, M. Golebiewski, T. Gorochowski, M. Hucka, S. Keating, C. Myers, D. Nickerson, F. Schreiber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>J Integr Bioinform. 2023 Mar 29;20(1):20230004. doi: 10.1515/jib-2023-0004. PMID: 36989443; PMCID: PMC10063176</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>P3 - König</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/36989443/"&gt;36989443&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1515/jib-2023-0004"&gt;10.1515/jib-2023-0004&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>J Integr Bioinform</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Editorial: Multiscale modeling for the liver</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ho H, Rezania V, Schwen LO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Front. Bioeng. Biotechnol. 2023 Apr 13;1179980. doi:10.3389/fbioe.2023.1179980</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>45029</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lars Ole Schwen</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P8 - Schwen</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37122862/"&gt;37122862&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3389/fbioe.2023.1179980 "&gt;10.3389/fbioe.2023.1179980 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Front Bioeng Biotechnol</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Eleven Strategies for Making Reproducible Research and Open Science Training the Norm at Research Institutions</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Friederike E. Kohrs, Susann Auer, Alexandra Bannach-Brown, Susann Fiedler, Tamarinde Haven, Verena Heise, Constance Holman, Flavio Azevedo, René Bernard, Arnim Bleier, Nicole Bössel, Brian Cahill, Leyla Jael Castro, Adrian Ehrenhofer, Kristina Eichel, Maximilian Frank, Claudia Frick, Malte Friese, Anne Gärtner, Kerstin Gierend, David Joachim Grüning, Lena Hahn, Maren Hülsemann, Malika Ihle, Sabrina Illius, Laura König, Matthias König, Louisa Kulke, Anton Kutlin, Fritjof Lammers, David M.A. Mehler, Christoph Miehl, Anett Müller-Alcazar, Claudia Neuendorf, Helen Niemeyer, Florian Pargent, Aaron Peikert, Christina U. Pfeuffer, Robert Reinecke, Jan Philipp Röer, Jessica L. Rohmann, Alfredo Sánchez-Tójar, Stefan Scherbaum, Elena Sixtus, Lisa Spitzer, Vera Maren Straßburger, Marcel Weber, Clarissa Whitmire, Josephine Zerna, Dilara Zorbek, Philipp Zumstein, Tracey L. Weissgerber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osfpreprints 2023.04.12.536571 doi: 10.7554/eLife.89736 </t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>45074</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>P3 - König</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37994903/"&gt;37994903&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.7554/eLife.89736 "&gt;10.7554/eLife.89736 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Automated Detection of Portal Fields and Central Veins in Whole-Slide Images of Liver Tissue</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Budelmann D, Laue H, Weis N, Dahmen U, D’Alessandro LA, Biermayer I, Klingmüller U, Ghallab A, Hassan R, Begher-Tibbe B, Hengstler JG, Schwen LO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Journal of Pathology Informatics 2022 13:100001, doi: 10.1016/j.jpi.2022.100001</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>44606</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>(None received QuaLiPerF funding for this work)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Stea-PK Mod</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/35242441/"&gt;35242441&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1016/j.jpi.2022.100001"&gt;10.1016/j.jpi.2022.100001&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Journal of Pathology Informatics</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Perfusion and T2 Relaxation Time as Predictors of Severity and Outcome in Sepsis-Associated Acute Kidney Injury: A Preclinical MRI Study</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Zhao, W.-T, Herrmann, K.-H., Sibgatulin R., Nahardani A., Krämer M., Heitplatz B., Van Marck V. , Reuter S., Reichenbach J.R., Hoerr V.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>J Magn Reson Imaging 2023 Apr 7. doi: 10.1002/jmri.28698</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>45111</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao, Karl-Heinz Herrmann, Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>P6 - Reichenbach</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37026419/"&gt;37026419&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1002/jmri.28698"&gt;10.1002/jmri.28698&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>J Magn Reson Imaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A pathway model of glucose-stimulated insulin secretion in the pancreatic β-cell</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Maheshvare MD., Raha S., König M.*, and Pal D.* (* equal contribution)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Front. Endocrinol. 14:1185656, doi: 10.3389/fendo.2023.1185656</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>44965</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>P3 - König</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37600713/"&gt;37600713&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3389/fendo.2023.1185656 "&gt;10.3389/fendo.2023.1185656 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Front Endocrinol</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Affine transformations accelerate the training of physics-informed neural networks of a one-dimensional consolidation problem</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Luis Mandl, André Mielke, Seyed Morteza Seyedpour, Tim Ricken</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Mandl, L., Mielke, A., Seyedpour, S.M. et al. Affine transformations accelerate the training of physics-informed neural networks of a one-dimensional consolidation problem. Sci Rep 13, 15566 (2023). https://doi.org/10.1038/s41598-023-42141-x</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E34" s="2" t="n">
+      <c r="D42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>45189</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>Luis Mandl, Tim Ricken</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>P7 - Ricken, SimLivA, ATLAS</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37730743/"&gt;37730743&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>&lt;a href="https://doi.org/10.1038/s41598-023-42141-x "&gt;10.1038/s41598-023-42141-x &lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Sci Rep</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Eleven Strategies for Making Reproducible Research and Open Science Training the Norm at Research Institutions</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Friederike E Kohrs, Susann Auer, Alexandra Bannach-Brown, Susann Fiedler, Tamarinde Laura Haven, Verena Heise, Constance Holman, Flavio Azevedo, René Bernard, Armin Bleier, Nicole Bössel, Brian Patrick Cahill, Leyla Jael Castro, Adrian Ehrenhofer, Kristina Eichel, Maximillian Frank, Claudia Frick, Malte Friese, Anne Gärtner, Kerstin Gierend, David Joachim Grüning, Lena Hahn, Maren Hülsemann, Malika Ihle, Sabrina Illius, Laura König, Matthias König, Louisa Kulke, Anton Kutlin, Fritjof Lammers, David MA Mehler, Christoph Miehl, Anett Müller-Alcazar, Claudia Neuendorf, Helen Niemeyer, Florian Pargent, Aaron Peikert, Christina U Pfeuffer, Robert Reinecke, Jan Philipp Röer, Jessica L Rohmann, Alfredo Sánchez-Tójar, Stefan Scherbaum, Elena Sixtus, Lisa Spitzer, Vera Maren Straßburger, Marcel Weber, Clarissa J Whitmire, Josephine Zerna, Dilara Zorbek, Philipp Zumstein, Tracey L Weissgerber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>eLife (2023) 12:e89736.</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>45253</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>P3 - König, SimLivA, ATLAS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/37994903/"&gt;37994903&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.7554/eLife.89736 "&gt;10.7554/eLife.89736 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>eLife</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SimLivA – Modelling ischemia reperfusion injury in the liver: A first step towards a clinical decision support tool.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hans-Michael Tautenhahn, Tim Ricken, Uta Dahmen, Luis Mandl, Laura Bütow, Steffen Gerhäusser, Lena Lambers, Xinpei Chen, Elina Lehmann, Olaf Dirsch, Matthias König</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GAMM-Mitteilungen. (2024), e202370003, 10.1002/gamm.202370003</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="1" t="n">
+        <v>45314</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hans-Michael Tautenhahn, Tim Ricken, Uta Dahmen, Luis Mandl, Laura Bütow, Steffen Gerhäusser, Lena Lambers, Xinpei Chen, Elina Lehmann, Olaf Dirsch, Matthias König</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König, P7 - Ricken, P9 - Tautenhahn, SimLivA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1002/gamm.202370003"&gt;10.1002/gamm.202370003&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>GAMM Mitteilungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cross-Species Variability in Lobular Geometry and Cytochrome P450 Hepatic Zonation: Insights into CYP1A2, CYP2E1, CYP2D6 and CYP3A4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mohamed Albadry, Jonas Kuettner, Jan Grzegorzewski, Olaf Dirsch, Eva Kindler, Robert Klopfleisch, Vaclav Liska, Vladimira Moulisova, Sandra Nickel, Richard Palek, Jachym Rosendorf, Sylvia Saalfeld, Utz Settmacher, Hans-Michael Tautenhahn, Matthias König, Uta Dahmen</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Front Pharmacol. 2024 May 16;15:1404938</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>45428</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Mohamed Albadry, Jonas Kuettner, Jan Grzegorzewski, Eva Kindler, Robert Klopfleisch, Sandra Nickel, Richard Palek, Sylvia Saalfeld, Hans-Michael Tautenhahn, Matthias König, Uta Dahmen</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38818378/"&gt;38818378&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3389/fphar.2024.1404938"&gt;10.3389/fphar.2024.1404938&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Front Pharmacol</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Bayesian modelling of time series data (BayModTS)-a FAIR workflow to process sparse and highly variable data</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Höpfl S, Albadry M, Dahmen U, Herrmann KH, Kindler EM, König M, Reichenbach JR, Tautenhahn HM, Wei W, Zhao WT, Radde NE.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bioinformatics. 2024 May 2;40(5):btae312</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Höpfl S, Albadry M, Dahmen U, Herrmann KH, Kindler EM, König M, Reichenbach JR, Tautenhahn HM, Wei W, Zhao WT, Radde NE.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König, P5 - Radde, P6 - Reichenbach, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38741151/"&gt;38741151&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1093/bioinformatics/btae312 "&gt;10.1093/bioinformatics/btae312 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>The simulation experiment description markup language (SED-ML): language specification for level 1 version 5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Smith LP, Bergmann FT, Garny A, Helikar T, Karr J, Nickerson D, Sauro H, Waltemath D, König M.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>J Integr Bioinform. 2024 Apr 15</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="1" t="n">
+        <v>45397</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>König M.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>P3 - König, Data Management</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38613325/"&gt;38613325&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1515/jib-2024-0008 "&gt;10.1515/jib-2024-0008 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>J iIntegr Bioinformatics</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Approaching thrombospondin-1 as a potential target for mesenchymal stromal cells to support liver regeneration after partial hepatectomy in mouse and humans</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tietze L*, Christ M*, Yu J, Stock P, Nickel S, Schulze A, Bartels M, Tautenhahn H-M*, Christ B*</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cells 2024, 13, doi: 10.3390/cells13060529 </t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>45537</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Christ M, Christ B</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>P1 - Christ, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38534373/"&gt;38534373&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3390/cells13060529 "&gt;10.3390/cells13060529 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Quantifying fat zonation in liver lobules: an integrated multiscale in silico model combining disturbed microperfusion and fat metabolism via a continuum biomechanical bi-scale, tri-phasic approach</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lena Lambers, Navina Waschinsky, Jana Schleicher, Matthias König, Hans-Michael Tautenhahn, Mohamed Albadry, Uta Dahmen, Tim Ricken </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Biomech Model Mechanobiol</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>45347</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lena Lambers, Matthias König, Hans-Michael Tautenhahn, Mohamed Albadry, Uta Dahmen, Tim Ricken</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König, P7 - Ricken, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38402347/"&gt;38402347&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1007/s10237-023-01797-0 "&gt;10.1007/s10237-023-01797-0 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Biomech Model Mechanobiol</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Quantifying Fat Zonation in Liver Lobules: An Integrated Multiscale In-silico Model Combining Disturbed Microperfusion and Fat Metabolism via a Continuum-Biomechanical Bi-scale, Tri-phasic Approach</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lena Lambers, Navina Waschinsky, Jana Schleicher, Matthias König, Hans-Michael Tautenhahn, Mohamed Albadry, Uta Dahmen and Tim Ricken</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Biomech Model Mechanobiol</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>45269</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lena Lambers, Matthias König, Hans-Michael Tautenhahn, Mohamed Albadry, Uta Dahmen, Tim Ricken</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König, P7 - Ricken, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38402347/"&gt;38402347&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1007/s10237-023-01797-0 "&gt;10.1007/s10237-023-01797-0 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Biomech Model Mechanobiol</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cross-Species Variability in Lobular Geometry and Cytochrome P450 Hepatic Zonation: Insights into CYP1A2, CYP2E1, CYP2D6 and CYP3A4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mohamed Albadry, Jonas Kuettner, Jan Grzegorzewski, Olaf Dirsch, Eva Kindler, Robert Klopfleisch, Vaclav Liska, Vladimira Moulisova, Sandra Nickel, Richard Palek, Jachym Rosendorf, Sylvia Saalfeld, Utz Settmacher, Hans-Michael Tautenhahn, Matthias König, Uta Dahmen</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bioRxiv 2023.12.28.573567, doi: https://doi.org/10.1101/2023.12.28.573567</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>45289</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Mohamed Albadry, Jonas Kuettner, Jan Grzegorzewski, Eva Kindler, Sandra Nickel, Sylvia Saalfeld, Hans-Michael Tautenhahn, Matthias König, Uta Dahmen</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/38818378/"&gt;38818378&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3389/fphar.2024.1404938 "&gt;10.3389/fphar.2024.1404938 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Front Pharmacol</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data report on gene expression after hepatic portal vein ligation (PVL) in rats</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Meyer D., Kosacka J., von Bergen M., Christ B., Marz M.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Frontiers in Genetics</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>45405</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Meyer D., Kosacka J., von Bergen M., Christ B., Marz M.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>P1 - Christ, P4 - Marz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/39233735/"&gt;39233735&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.3389/fgene.2024.1421955 "&gt;10.3389/fgene.2024.1421955 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Front Genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Marginal Percentile Intervals in Bayesian Inference are Overconfident</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Tautenhahn Hans-Michael, Wagner Vincent, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="1" t="n">
+        <v>45513</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Tautenhahn Hans-Michael, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>P5 - Radde, P9 - Tautenhahn</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/-/"&gt;-&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/-"&gt;-&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Specifications of standards in systems and synthetic biology: status, developments, and tools in 2024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Martin Golebiewski, Gary Bader, Padraig Gleeson, Thomas E Gorochowski, Sarah M Keating, Matthias König, Chris J Myers, David P Nickerson, Björn Sommer, Dagmar Waltemath, Falk Schreiber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> J Integr Bioinform. 2024 Jul 22. doi: 10.1515/jib-2024-0015</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="1" t="n">
+        <v>45495</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>P3 - König, SimLivA, ATLAS</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/39026464/"&gt;39026464&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1515/jib-2024-0015 "&gt;10.1515/jib-2024-0015 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>J iIntegr Bioinformatics</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A sphingolipid rheostat controls apoptosis versus apical cell extrusion as alternative tumour-suppressive mechanisms</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Armistead Joy, Höpfl Sebastian, Goldhausen Pierre, Müller-Hartmann Andrea, Fahle Evelin, Hatzold Julia, Franzen Rainer, Brodesser Susanne, Radde Nicole E, Hammerschmidt Matthias</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Cell Death and Disease</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="1" t="n">
+        <v>45579</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole E</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/39397024/"&gt;39397024&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1038/s41419-024-07134-2 "&gt;10.1038/s41419-024-07134-2 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Cell Death and Disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A quality assurance protocol for reliable and reproducible multi-TI arterial spin labeling perfusion imaging in rat livers</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao, Karl-Heinz Herrmann, Weiwei Wei, Martin Krämer, Uta Dahmen &amp; Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Magnetic Resonance Materials in Physics, Biology and Medicine, DOI:10.1007/s10334-024-01223-1 </t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>45661</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao, Karl-Heinz Herrmann, Weiwei Wei, Martin Krämer, Uta Dahmen &amp; Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>P6 - Reichenbach, P2-Dahmen</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://pubmed.ncbi.nlm.nih.gov/39754650/"&gt;39754650&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1007/s10334-024-01223-1 "&gt;10.1007/s10334-024-01223-1 &lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>MAGMA</t>
         </is>
       </c>
     </row>
@@ -2446,46 +3568,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Authors Qualiperf</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
@@ -2507,7 +3629,7 @@
           <t>Preprints 2021, 2021080303, https://www.preprints.org/manuscript/202108.0303/v1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -2547,7 +3669,7 @@
           <t xml:space="preserve">arXiV, 2021, 2106.00844, [Submitted to Bioinformatics 2021-06-02] </t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>43984</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -2587,7 +3709,7 @@
           <t>bioRxiv doi: https://doi.org/10.1101/245076</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>44648</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -2627,7 +3749,7 @@
           <t>Preprints 2022, 2022060137 (doi: 10.20944/preprints202206.0137.v1).</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>44721</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -2667,7 +3789,7 @@
           <t>medRxiv 2023.02.01.23285358; doi: https://doi.org/10.1101/2023.02.01.23285358</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -2707,7 +3829,7 @@
           <t>bioRxiv 2023.03.21.512712; doi: https://doi.org/10.1101/2023.03.21.512712</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>45012</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -2747,7 +3869,7 @@
           <t>bioRxiv 2023.04.12.536571; doi: https://doi.org/10.1101/2023.04.12.536571</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -2774,30 +3896,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eleven Strategies for Making Reproducible Research and Open Science Training the Norm at Research Institutions</t>
+          <t>Insights into Intestinal P-glycoprotein Function using Talinolol: A PBPK Modeling Approach</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Friederike E. Kohrs, Susann Auer, Alexandra Bannach-Brown, Susann Fiedler, Tamarinde Haven, Verena Heise, Constance Holman, Flavio Azevedo, René Bernard, Arnim Bleier, Nicole Bössel, Brian Cahill, Leyla Jael Castro, Adrian Ehrenhofer, Kristina Eichel, Maximilian Frank, Claudia Frick, Malte Friese, Anne Gärtner, Kerstin Gierend, David Joachim Grüning, Lena Hahn, Maren Hülsemann, Malika Ihle, Sabrina Illius, Laura König, Matthias König, Louisa Kulke, Anton Kutlin, Fritjof Lammers, David M.A. Mehler, Christoph Miehl, Anett Müller-Alcazar, Claudia Neuendorf, Helen Niemeyer, Florian Pargent, Aaron Peikert, Christina U. Pfeuffer, Robert Reinecke, Jan Philipp Röer, Jessica L. Rohmann, Alfredo Sánchez-Tójar, Stefan Scherbaum, Elena Sixtus, Lisa Spitzer, Vera Maren Straßburger, Marcel Weber, Clarissa Whitmire, Josephine Zerna, Dilara Zorbek, Philipp Zumstein, Tracey L. Weissgerber</t>
+          <t>Beatrice Stemmer Mallol, Jan Grzegorzewski, Matthias König</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>osfpreprints 2023.04.12.536571 doi: 10.31219/osf.io/kcvra</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>45074</v>
+          <t>bioRxiv 2023.11.21.568168; doi: https://doi.org/10.1101/2023.11.21.568168</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11/23/2023</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Matthias König</t>
+          <t>Jan Grzegorzewski, Matthias König</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2807,28 +3931,30 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.31219/osf.io/kcvra"&gt;10.31219/osf.io/kcvra&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/-"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Quantifying Fat Zonation in Liver Lobules: An Integrated Multiscale In-silico Model Combining Disturbed Microperfusion and Fat Metabolism via a Continuum-Biomechanical Bi-scale, Tri-phasic Approach</t>
+          <t>Simulation of zonation-function relationships in the liver using coupled multiscale models: Application to drug-induced liver injury</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lena Lambers, Navina Waschinsky, Jana Schleicher, Matthias König, Hans-Michael Tautenhahn, Mohamed Albadry, Uta Dahmen and Tim Ricken</t>
+          <t>Steffen Gerhäusser, Lena Lambers, Luis Mandl, Julian Franquinet, Tim Ricken, Matthias König</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Research Square</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>45269</v>
+          <t>bioRxiv 2024.03.26.586870; doi: https://doi.org/10.1101/2024.03.26.586870</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3/29/2024</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2837,17 +3963,207 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lena Lambers, Matthias König, Hans-Michael Tautenhahn, Mohamed Albadry, Uta Dahmen, Tim Ricken</t>
+          <t>Steffen Gerhäusser, Lena Lambers, Tim Ricken, Matthias König</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>P2 - Dahmen, P3 - König, P7 - Ricken, P9 - Tautenhahn</t>
+          <t>P3 - König, P7 - Ricken</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;a href="https://doi.org/10.21203/rs.3.rs-3348101/v1"&gt;10.21203/rs.3.rs-3348101/v1&lt;/a&gt;</t>
+          <t>&lt;a href="https://doi.org/-"&gt;-&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EFECT – A Method and Metric to Assess the Reproducibility of Stochastic Simulation Studies</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T.J. Sego, Matthias König, Luis L. Fonseca, Baylor Fain, Adam C. Knapp, Krishna Tiwari, Henning Hermjakob, Herbert M. Sauro, James A. Glazier, Reinhard C. Laubenbacher, Rahuman S. Malik-Sheriff</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>arXiv:2406.16820; 10.48550/arXiv.2406.16820</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6/24/2024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>P3 - König</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.48550/arXiv.2406.16820"&gt;10.48550/arXiv.2406.16820&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Joint zonated quantification of multiple parameters in hepatic lobules</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Laue* HOA, Budelmann* D, Albadry* M, Engel C, Weiss N, Dahmen* U, Schwen* LO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ResearchSquare, doi: 10.21203/rs.3.rs-4764718/v1, 2024</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Budelmann* D, Albadry* M, Dahmen* U, Schwen* LO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P8 - Schwen, Stea-PK Mod</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.21203/rs.3.rs-4764718/v1"&gt;10.21203/rs.3.rs-4764718/v1&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FROG Analysis Ensures the Reproducibility of Genome Scale Metabolic Models</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Karthik Raman, Miroslav Kratochvil, Brett G. Olivier, Matthias König, Pratyay Sengupta, Dinesh Kumar Kuppa Baskaran, Tung V N Nguyen, Daniel Lobo, St Elmo Wilken, Krishna Kumar Tiwari, Aswathy K. Raghu, Indumathi Palanikumar, Lavanya Raajaraam, Maziya Ibrahim, Sanjaay Balakrishnan, Shreyansh Umale, Frank Bergmann, Tanisha Malpani, Venkata P Satagopam, Reinhard Schneider, Moritz E. Beber, Sarah Keating, Mihail Anton, Alina Renz, Meiyappan Lakshmanan, Dong-Yup Lee, Lokanand Koduru, Reihaneh Mostolizadeh, Oscar Dias, Emanuel Cunha, Alexandre Oliveira, Yi Qing Lee, Karsten Zengler, Rodrigo Santibanez-Palominos, Manish Kumar, Matteo Barberis, Bhanwar Lal Puniya, Tomas Helikar, Hoang V. Dinh, Patrick F. Suthers, Costas D. Maranas, Isabella Casini, Seyed Babak Loghmani, Nadine Veith, Nantia Leonidou, Feiran Li, Yu Chen, Jens Nielsen, GaRyoung Lee, Sang Mi Lee, Gi Bae Kim, Pedro T. Monteiro, Miguel C. Teixeira, Hyun Uk Kim, Sang Yup Lee, Ulf W. Liebal, Lars M. Blank, Christian Lieven, Chaimaa Tarzi, Claudio Angione, Manga Enuh Blaise, Celik Pinar Aytar, Mikhail Kulyashov, llya Akberdin, Dohyeon Kim, Sung Ho Yoon, Zhaohui Xu, Jyotshana Gautam, William T. Scott Jr., Peter J. Schaap, Jasper J. Koehorst, Cristal Zuniga, Gabriela Canto-Encalada, Sara Benito-Vaquerizo, Ivette Parera Olm, Maria Suarez-Diez, Qianqian Yuan, Hongwu Ma, Mohammad Mazharul Islam, Jason A. Papin, Francisco Zorrilla, Kiran Raosaheb Patil, Arianna Basile, Juan Nogales, Granado San Leon, Freddy Castillo-Alfonso, Roberto Olivares-Hernandez, Gabriel Vigueras-Ramirez, Henning Hermjakob, Andreas Drager, Rahuman S Malik-Sheriff</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bioRxiv 2024.09.24.614797; 10.1101/2024.09.24.614797</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9/24/2024</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>P3 - König, Data Management, SimLivA, ATLAS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/10.1101/2024.09.24.614797 "&gt;10.1101/2024.09.24.614797 &lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Eulerian Parameter Inference: A Probabilistic Change of Variables for Model-Based Inference with High-Variability Data Sets</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wagner Vincent, Castellaz Benjamin, Kaiser Lars, Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ResearchSquare</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45599</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/-"&gt;-&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Integrated mathematical and experimental modeling uncovers enhanced EMT plasticity upon loss of the DLC1 tumor suppressor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Höpfl et al.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://doi.org/-"&gt;-&lt;/a&gt;</t>
         </is>
       </c>
     </row>
@@ -2866,32 +4182,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Authors Qualiperf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
@@ -2908,7 +4224,7 @@
           <t xml:space="preserve">*Wagner Vincent, *Höpfl Sebastian, Klingel Viviane, Pop Maria C. , Radde Nicole E. </t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>44664</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -2938,7 +4254,7 @@
           <t>Budelmann D, Cao Q, Laue H, Albadry M, Dahmen U, Schwen LO</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>45081</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -2968,41 +4284,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Authors Qualiperf</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
@@ -3024,7 +4340,7 @@
           <t>Helen Leal Pujol, Matthias König</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>44684</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -3059,7 +4375,7 @@
           <t>Fritz Otlinghaus, Steffen Gerhäusser, Ishaan Desai, Tim Ricken, Benjamin Uekermann</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -3094,7 +4410,7 @@
           <t>Lambers, Lena</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>45006</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -3129,7 +4445,7 @@
           <t>Beatrice Stemmer Mallol, Matthias König (supervisor)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>45124</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -3164,7 +4480,7 @@
           <t>Jan Grzegorzewski, Matthias König</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>45179</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -3182,6 +4498,95 @@
           <t>P3 - König</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Master thesis</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quantitative Image Analysis of Hepatic Zonation in Cytochrome P450 and Steatosis Using Whole Slide Scans</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jonas Küttner (supervisor: Matthias König)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8/28/2024</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jonas Küttner (supervisor: Matthias König)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P3 - König</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thesis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Exploring Alterations in Kidney Function and Tissue Properties Following Sepsis-Induced Acute Kidney Injury with Quantitative Multi-Parametric MRI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45699</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thesis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Reproducible Modeling and Uncertainty Quantification of Sparse and Variable Data</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sebastian Höpfl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3194,41 +4599,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Conference</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Authors Qualiperf</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
@@ -3250,7 +4655,7 @@
           <t>24. Chirurgische Forschungstage, CFT2021, https://forschungstage2021.de/</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -3285,7 +4690,7 @@
           <t xml:space="preserve"> 24te Chirurgische Forschungstage, CFT2021, https://forschungstage2021.de/</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>44441</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -3320,7 +4725,7 @@
           <t>8th international conference on Systems Biology of Mammalian Cells SBMC 2022, https://sbmc2022.de/</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>44698</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -3355,7 +4760,7 @@
           <t xml:space="preserve">SimTech Status Seminar </t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>44481</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -3390,7 +4795,7 @@
           <t>SimTech Status Seminar 2022, Bad Boll</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>44747</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -3425,7 +4830,7 @@
           <t>Simtech Status Seminar 2022</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>44746</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -3460,7 +4865,7 @@
           <t>SimTech Status-Seminar Bad Boll 2022</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>44746</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -3495,7 +4900,7 @@
           <t>Pints&amp;Posters, 15.07.2022, University of Stuttgart</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -3530,7 +4935,7 @@
           <t>SimTech Status Seminar 2022, Bad Boll</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="1" t="n">
         <v>44746</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -3565,7 +4970,7 @@
           <t>Current Trends in Systems and Control Theory, June 7 2022 Stuttgart</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="1" t="n">
         <v>44719</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -3600,7 +5005,7 @@
           <t>German Conference on Bioinformatics 2022, https://gcb2022.de/</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="1" t="n">
         <v>44810</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -3635,7 +5040,7 @@
           <t>Inventing the Future - University of Stuttgart meets Bosch</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="1" t="n">
         <v>44858</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -3670,7 +5075,7 @@
           <t>International Society for Magnetic Resonance in Medicine 2023, https://www.ismrm.org/23m/</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -3705,7 +5110,7 @@
           <t>Treffen der Joachim-Herz-Stiftung, 10.-11.20.2023 in Hamburg</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="1" t="n">
         <v>44968</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -3727,21 +5132,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>The influence of marginal organs on the drug metabolism in liver transplantation</t>
+          <t>Endoglin and Soluble Endoglin Modulation in NASH: Therapeutic Potential of Monoclonal Antibody Intervention</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bütow L.B., Tautenhahn H.-M. T., Schröter D.S., Schlattmann P.S., Settmacher U.S., Dahmen U.D.,</t>
+          <t>Samira Eissazadeh, Jana Rathouská, Ivana Němečková, Seyedeh Niloufar Mohammadi, Matthias König, Petr Nachtigal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASL European Association for the Study of the Liver, https://www.easlcongress.eu,</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>45101</v>
+          <t>27. kongres o ateroskleróze</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44938</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3750,33 +5155,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Laura Bütow, Hans-Michael Tautenhahn. T., Schröter D.S., Uta Dahmen</t>
+          <t>Matthias König</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P2 - Dahmen, P9 - Tautenhahn, SimLivA</t>
+          <t>P3 - König, SimLivA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Influence of marginal organs on the drug metabolism in liver transplantation. Outline for a prospective clinical study</t>
+          <t>The influence of marginal organs on the drug metabolism in liver transplantation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bütow L.B., Schröter D.S., Tautenhahn H.-M. T., Dahmen U.D., Nickel S. N.,</t>
+          <t>Bütow L.B., Tautenhahn H.-M. T., Schröter D.S., Schlattmann P.S., Settmacher U.S., Dahmen U.D.,</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>33., Wilseder Workshop von Biotest- Individulaisierte Therapie von Lebererkrnakungen, https://www.biotest-wilsede.de,</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>45105</v>
+          <t>EASL European Association for the Study of the Liver, https://www.easlcongress.eu,</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45101</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3785,7 +5190,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laura Bütow, Schröter D.S., Hans-Michael Tautenhahn, Uta Dahmen</t>
+          <t>Laura Bütow, Hans-Michael Tautenhahn. T., Schröter D.S., Uta Dahmen</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3797,21 +5202,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Time-series of transcriptome data reveal non-coding RNAs can be incorporated into modelling approaches</t>
+          <t>Influence of marginal organs on the drug metabolism in liver transplantation. Outline for a prospective clinical study</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meyer D., Barth E., Christ B., König M., Marz M.</t>
+          <t>Bütow L.B., Schröter D.S., Tautenhahn H.-M. T., Dahmen U.D., Nickel S. N.,</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Workshop on Computational Models in Biology and Medicine 2023</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>45092</v>
+          <t>33., Wilseder Workshop von Biotest- Individulaisierte Therapie von Lebererkrnakungen, https://www.biotest-wilsede.de,</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45105</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3820,33 +5225,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Daria Meyer, Bruno Christ, Matthias König, Manja Marz</t>
+          <t>Laura Bütow, Schröter D.S., Hans-Michael Tautenhahn, Uta Dahmen</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P1 - Christ, P3 - König, P4 - Marz</t>
+          <t>P2 - Dahmen, P9 - Tautenhahn, SimLivA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Digital Liver Twin - Data- and Model-Driven Multiscale Liver Modeling</t>
+          <t>Time-series of transcriptome data reveal non-coding RNAs can be incorporated into modelling approaches</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tim Ricken, Steffen Gerhäusser, Lena Lambers, Luis Mandl</t>
+          <t>Meyer D., Barth E., Christ B., König M., Marz M.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>International Conference on Data-Integrated Simulation Science (SimTech2023), https://www.simtech2023.uni-stuttgart.de/, 04. - 06. Oktober 2023, Sutttgart</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>45056</v>
+          <t>Workshop on Computational Models in Biology and Medicine 2023</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45092</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3855,101 +5260,356 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tim Ricken, Steffen Gerhäusser, Lena Lambers, Luis Mandl</t>
+          <t>Daria Meyer, Bruno Christ, Matthias König, Manja Marz</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P7 - Ricken</t>
+          <t>P1 - Christ, P3 - König, P4 - Marz</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GlucoCEST MRI to Assess Alterations in the Corticomedullary Glucose Gradient in a Rat Model of S-AKI</t>
+          <t>Digital Liver Twin - Data- and Model-Driven Multiscale Liver Modeling</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan-Ting Zhao, Karl-Heinz Herrmann, Jürgen R. Reichenbach and Verena Hoerr </t>
+          <t>Tim Ricken, Steffen Gerhäusser, Lena Lambers, Luis Mandl</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25th DS-ISMRM (Germany chapter International Society for Magnetic Resonance in Medicine), Berlin, 6-7 September, 2023, Poster</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>International Conference on Data-Integrated Simulation Science (SimTech2023), https://www.simtech2023.uni-stuttgart.de/, 04. - 06. Oktober 2023, Sutttgart</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45056</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tim Ricken, Steffen Gerhäusser, Lena Lambers, Luis Mandl</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>P7 - Ricken</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Adaptive Response of Liver Perfusion in Preclinical Portal Vein Ligation</t>
+          <t>GlucoCEST MRI to Assess Alterations in the Corticomedullary Glucose Gradient in a Rat Model of S-AKI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wan-Ting Zhao, Weiwei Wei, Karl-Heinz Herrmann, Martin Krämer, Uta Dahmen, Jürgen R. Reichenbach</t>
+          <t xml:space="preserve">Wan-Ting Zhao, Karl-Heinz Herrmann, Jürgen R. Reichenbach and Verena Hoerr </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>39th European Society for Magnetic Resonance in Medicine and Biology, Basel, Switzerland. Poster LB280</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>45056</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Wan-Ting Zhao, Weiwei Wei, Karl-Heinz Herrmann, Uta Dahmen, Jürgen R. Reichenbach</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>P2 - Dahmen, P6 - Reichenbach</t>
-        </is>
-      </c>
+          <t>25th DS-ISMRM (Germany chapter International Society for Magnetic Resonance in Medicine), Berlin, 6-7 September, 2023, Poster</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Adaptive Response of Liver Perfusion in Preclinical Portal Vein Ligation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao, Weiwei Wei, Karl-Heinz Herrmann, Martin Krämer, Uta Dahmen, Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>39th European Society for Magnetic Resonance in Medicine and Biology, Basel, Switzerland. Poster LB280</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45056</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao, Weiwei Wei, Karl-Heinz Herrmann, Uta Dahmen, Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P6 - Reichenbach</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>FAIR Bayesian Optimal Experimental Design in Systems Biology</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Höpfl Sebastian, Wagner Vincent, Guizeni Eya, Pleiss Jürgen, Range Jan, Radde Nicole</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>International Conference on Data-Integrated Simulation Science (SimTech2023), https://www.simtech2023.uni-stuttgart.de/</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D23" s="1" t="n">
         <v>45087</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Sebastian Höpfl, Nicole Erika Radde</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Robust Rat Liver Lobe Segmentation in Low-SNR T2-weighted Datasets Using a 2.5D Approach</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Wei-Chan Hsu, Wan-Ting Zhao, Karl-Heinz Herrmann, Daniel Güllmar, Weiwei Wei, Uta Dahmen, Kai Lawonn, Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2024 International Society for Magnetic Resonance in Medicine, Singapore, 04-09.05.24</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1/26/2024</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Wan-Ting Zhao, Karl-Heinz Herrmann, Weiwei Wei, Uta Dahmen, Jürgen R. Reichenbach</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P6 - Reichenbach</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Captopril in Focus: Establishing an Open Pharmacokinetic Dataset and PBPK Modeling</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mariia Myshkina, Matthias König</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PAGE2024, 32nd meeting, 26-28 June, 2024 Population Approach Group Europe</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45449</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>P3 - König, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PK-LLM : Large Language Model (LLM) for Pharmacokinetic (PK) Data Curation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Prerna Parakkat, Matthias König</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HIC conference 2024, Humboldt Internship Program Day, Berlin, 18 July 2024</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7/18/2024</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>P3 - König, SimLivA, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Canagliflozin</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vera Tereshchuk, Matthias König</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HIC conference 2024, Humboldt Internship Program Day, Berlin, 18 July 2024</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7/18/2024</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>P3 - König, SimLivA, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A physiologically based pharmacokinetic model of morphine</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deepa Maheshvare M., Rohini Chakraborty, Rohit Chakraborty, Matthias König</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HIC conference 2024, Humboldt Internship Program Day, Berlin, 18 July 2024</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7/18/2024</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>P3 - König, SimLivA, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BayModTS: A Bayesian workflow to process variable and sparse time series data.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SBMC 2024, https://www.lisym-cancer.org/sbmc2024</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5/14/2024</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes, No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>P5 - Radde</t>
         </is>
@@ -3966,41 +5626,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Conference</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Authors Qualiperf</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
@@ -4022,7 +5682,7 @@
           <t>24. Chirurgische Forschungstage, CFT2021, https://forschungstage2021.de/</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>44441</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -4057,7 +5717,7 @@
           <t>24te Chirurgische Forschungstage, CFT2021, https://forschungstage2021.de/</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -4092,7 +5752,7 @@
           <t>ISMRM</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>44510</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -4123,7 +5783,7 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>44510</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -4158,7 +5818,7 @@
           <t>The 8th European Congress on Computational Methods in Applied Sciences and Engineering ECCOMAS Congress 2022</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>44717</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -4193,7 +5853,7 @@
           <t>15th World Congress on Computational Mechanics (WCCM-XV) 8th Asian Pacific Congress on Computational Mechanics (APCOM-VIII)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -4228,7 +5888,7 @@
           <t>Jahrestagung der mitteldeutschen Viszeralmedizin</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -4263,7 +5923,7 @@
           <t>BioMechBW Symposium, 19.07.2022, Tübingen</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="1" t="n">
         <v>44761</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -4298,7 +5958,7 @@
           <t>92nd Annual Meeting of the International Association of Applied Mathematics and Mechanics (GAMM)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="1" t="n">
         <v>44789</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -4333,7 +5993,7 @@
           <t>GACM Congress, Essen</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="1" t="n">
         <v>44826</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -4368,7 +6028,7 @@
           <t>ICSB2022, The 21st International Conference on Systems Biology</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="1" t="n">
         <v>44831</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -4403,7 +6063,7 @@
           <t>GAMM Annual Meeting 2022 ,https://jahrestagung.gamm-ev.de/</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="1" t="n">
         <v>44791</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -4438,7 +6098,7 @@
           <t>Combine Meeting, Satellite Event to the ICSB Conference, October 6-7, 2022, Berlin</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="1" t="n">
         <v>44840</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -4473,7 +6133,7 @@
           <t>3rd EnzymeML Workshop, October 18-19, 2022, Rüdesheim</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="1" t="n">
         <v>44852</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -4508,7 +6168,7 @@
           <t>BioSB 2023, https://www.aanmelder.nl/biosb2023, Egmond aan Zee</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -4543,7 +6203,7 @@
           <t>Workshop on Computational Models in Biology and Medicine 2023, http://www.biometrische-gesellschaft.de/arbeitsgruppen/statistische-methoden-i-d-bioinformatik/workshop2023.html</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="1" t="n">
         <v>45092</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -4578,7 +6238,7 @@
           <t>International Conference on Systems Biology of Human Disease, https://www.sbhdberlin.org/index.html</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="1" t="n">
         <v>45096</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -4613,7 +6273,7 @@
           <t>31st Conference on Intelligent Systems for Molecular Biology (ISMB), https://www.iscb.org/ismbeccb2023</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="1" t="n">
         <v>45130</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -4648,7 +6308,7 @@
           <t>International Conference on Data-Integrated Simulation Science (SimTech2023), https://www.simtech2023.uni-stuttgart.de/</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="1" t="n">
         <v>45203</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -4683,7 +6343,7 @@
           <t>SIAM CSE, Amsterdam, 26.02.2023 - 03.03.2023</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -4718,7 +6378,7 @@
           <t>GAMM Fachausschuss Computational Biomechanics, 13.-14.02.2023 in Saarbrücken</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="1" t="n">
         <v>44970</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -4753,7 +6413,7 @@
           <t>MBM2023 - Workshop on Modelling in Biology and Medicine - https://mbm.systemsbiology.se</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="1" t="n">
         <v>45063</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -4788,7 +6448,7 @@
           <t>ISMB/ECCB 2023 Conference on Intelligent Systems for Molecular Biology (ISMB) and European Conference on Computational Biology (ECCB)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="1" t="n">
         <v>45131</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -4823,7 +6483,7 @@
           <t>93. Jahrestagung der Gesellschaft für angewandte Mathematik und Mechanik; https://jahrestagung.gamm-ev.de/</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="1" t="n">
         <v>44963</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -4858,7 +6518,7 @@
           <t>93. Jahrestagung der Gesellschaft für angewandte Mathematik und Mechanik (GAMM), Dresden</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="1" t="n">
         <v>45076</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -4893,7 +6553,7 @@
           <t>Workshop on Computational Models in Biology and Medicine 2023</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -4928,7 +6588,7 @@
           <t>93rd Annual Meeting of the International Association of Applied Mathematics and Mechanics, https://jahrestagung.gamm.org/annual-meeting-2023</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="1" t="n">
         <v>44963</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -4963,7 +6623,7 @@
           <t>SPP2311 - Annual Workshop Magdeburg</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="1" t="n">
         <v>45269</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -4998,7 +6658,7 @@
           <t>X International Conference on Computational Bioengineering, Wien, 20.-22.09.2023, https://iccb2023.conf.tuwien.ac.at/</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -5033,7 +6693,7 @@
           <t>AstraZeneca Seminar</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="1" t="n">
         <v>44935</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -5068,7 +6728,7 @@
           <t>ICCB2023 - X International Conference on Computational Bioengineering</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -5103,7 +6763,7 @@
           <t>ITB - Institute for Theoretical Biology, Humboldt-University Berlin</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="1" t="n">
         <v>45209</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -5138,7 +6798,7 @@
           <t>e:Med Meeting 2023 on Systems Medicine</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="1" t="n">
         <v>45209</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -5154,6 +6814,253 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>P3 - König, SimLivA, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Reproducible digital twins for personalized liver function assessment</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COMBINE2024, Stuttgart</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>P3 - König, Data Management, SimLivA, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Computational Model Development Using SBML: sbmlutils, sbm4humans, cy3sbml</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>COMBINE 2024, Stuttgart</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45360</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>P3 - König, Data Management, SimLivA, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Modulation of endoglin and soluble endoglin in NASH: Computational modeling and monoclonal antibody therapeutic benefits</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Samira Eissazadeh, Jana Urbankova Rathouska, Ivana Nemeckova, Matthias König, Petr Nachtigal</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8/20/2024</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Matthias König</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>P3 - König, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A reproducible Bayesian workflow to integrate discrete time series data into continuous models</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Workshop on Computational Models in Biology and Medicine 2024, https://www.biometrische-gesellschaft.de/arbeitsgruppen/statistische-methoden-i-d-bioinformatik/workshop2024.html</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45479</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BayModTS: A FAIR Bayesian workflow to process variable and sparse time series data.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VPH 2024, https://vph-conference.org/</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>45391</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Design of Experiments for Enzyme Kinetics</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EnzymeML 5th Workshop, https://www.beilstein-institut.de/en/projects/strenda/meetings/5th-enzymeml-workshop/</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9/24/2024</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A reproducible Bayesian workflow for analyzing highly heterogeneous time-resolved medical data</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SIAM Conference on Uncertainty Quantification (UQ24), https://www.siam.org/conferences/cm/conference/uq24</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2/27/2024</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Höpfl Sebastian, Radde Nicole</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
         </is>
       </c>
     </row>
@@ -5168,36 +7075,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Qualiperf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
@@ -5219,7 +7126,7 @@
           <t>Bruno Christ, Uta Dahmen, Nicole Radde, Tim Ricken</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -5249,7 +7156,7 @@
           <t>Tim Ricken, Oliver Röhrle, Silvia Budday</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -5279,7 +7186,7 @@
           <t>Tim Ricken, Oliver Röhrle, Silvia Budday</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>44717</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -5309,7 +7216,7 @@
           <t>Ho H, Rezaina V, Schwen LO</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>44516</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -5339,7 +7246,7 @@
           <t>Christian Bleiler, Lena Lambers, Renate Sachse</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>44825</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -5369,7 +7276,7 @@
           <t xml:space="preserve">Christ B, Oertel M </t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -5399,7 +7306,7 @@
           <t xml:space="preserve">Lena Lambers, Uta Dahmen </t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -5429,7 +7336,7 @@
           <t xml:space="preserve">Nicole Radde, Sebastian Höpfl </t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -5459,7 +7366,7 @@
           <t>Hans-Michael Tautenhahn</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -5489,7 +7396,7 @@
           <t>Hans-Michael Tautenhahn</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -5519,7 +7426,7 @@
           <t>Hans-Michael Tautenhahn</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -5536,7 +7443,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workshop Leader </t>
+          <t xml:space="preserve">Workshop </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5549,7 +7456,7 @@
           <t xml:space="preserve">Nicole Radde, Ingmar Glauche </t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="1" t="n">
         <v>44760</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -5579,7 +7486,7 @@
           <t>Nicole Radde</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -5609,7 +7516,7 @@
           <t>Tim Ricken</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -5639,7 +7546,7 @@
           <t>Jürgen Reichenbach</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -5669,7 +7576,7 @@
           <t>Matthias König</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="1" t="n">
         <v>44858</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -5699,7 +7606,7 @@
           <t>Professorin Dr. Uta Dahmen, Professor Dr.-Ing. Tim Ricken, Privatdozent Dr. Hans-Michael Tautenhahn, Dr. Matthias König</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="1" t="n">
         <v>44181</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -5729,7 +7636,7 @@
           <t>Professor Dr.-Ing. Tim Ricken, Professor Dr. Steffen Staab, Privatdozent Dr. Hans-Michael Tautenhahn, Dr. Matthias König</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="1" t="n">
         <v>44819</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -5759,7 +7666,7 @@
           <t>König Matthias</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="1" t="n">
         <v>44964</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -5789,7 +7696,7 @@
           <t>König Matthias</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="1" t="n">
         <v>44969</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -5819,7 +7726,7 @@
           <t>König Matthias</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="1" t="n">
         <v>44964</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -5849,7 +7756,7 @@
           <t>Budelmann D, Laue H, Weis N, Dahmen U, D’Alessandro LA, Biermayer I, Klingmüller U, Ghallab A, Hassan R, Begher-Tibbe B, Hengstler JG, Schwen LO</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="1" t="n">
         <v>44420</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -5879,7 +7786,7 @@
           <t>Budelmann D, Cao Q, Laue H, Albadry M, Dahmen U, Schwen LO</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="1" t="n">
         <v>45050</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -5909,7 +7816,7 @@
           <t>Radde Nicole, Waltemath Dagmar, Höpfl Sebastian</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="1" t="n">
         <v>45300</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -5939,7 +7846,7 @@
           <t>Radde Nicole</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="1" t="n">
         <v>45056</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -5969,7 +7876,7 @@
           <t>Mandl L., Gerhäusser S., Lambers L., König M., Tautenhahn H.-M., Dahmen U., Ricken T.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="1" t="n">
         <v>45227</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -5980,6 +7887,98 @@
       <c r="F27" t="inlineStr">
         <is>
           <t>P2 - Dahmen, P3 - König, P7 - Ricken, P9 - Tautenhahn, SimLivA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Internship report</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A physiologically-based pharmacokinetic (PBPK) model of sorafenib for investigating the effect of sorafenib parameters in hepatorenal impairment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Frances Okibedi, Matthias König</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>P3 - König, ATLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dataset for "Joint zonated quantification of multiple parameters in hepatic lobules"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Laue HOA, Budelmann D, Albadry M, Engel C, Weiss N, Dahmen U, Schwen LO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7/25/2024</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>P2 - Dahmen, P8 - Schwen, Stea-PK Mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Organization and hosting COMBINE 2024 Meeting in Stuttgart</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>COMBINE 2024</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Radde Nicole, Höpfl Sebastian</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45300</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>P5 - Radde</t>
         </is>
       </c>
     </row>
